--- a/output/full_scan/batch_seq5_2026-06-05.xlsx
+++ b/output/full_scan/batch_seq5_2026-06-05.xlsx
@@ -527,21 +527,21 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>5328</v>
+        <v>5536</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>華容</t>
+          <t>聖暉*</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
         <v/>
       </c>
       <c r="D2" s="2" t="n">
-        <v>910.7696368380188</v>
+        <v>1052.034965998322</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>40.7</v>
+        <v>1130</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
@@ -552,49 +552,49 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>72.79510184083455</v>
+        <v>67.12442365234762</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>33.48961209011014</v>
+        <v>31.02352731129143</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>1.576963683801872</v>
+        <v>1.203496599832183</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M2" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.4318581396134555</v>
+        <v>8.464584055521001</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>4542</v>
+        <v>5328</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>科嶠</t>
+          <t>華容</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>806.5970268783533</v>
+        <v>1050.769636838019</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>286</v>
+        <v>40.7</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -605,16 +605,16 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>65.26226355887599</v>
+        <v>72.79510184623118</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>39.07907780242496</v>
+        <v>33.48961203331253</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>3.659702687835325</v>
+        <v>1.576963683801872</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" s="2" t="n">
         <v>0</v>
@@ -623,31 +623,31 @@
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>-0.4706831989053164</v>
+        <v>0.4318581396706911</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>5228</v>
+        <v>6112</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>鈺鎧</t>
+          <t>邁達特</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>787.0041728573112</v>
+        <v>1042.527934502536</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>69.40000000000001</v>
+        <v>50</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -658,16 +658,16 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>77.71978076530142</v>
+        <v>69.35692577246097</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>48.81271724363551</v>
+        <v>22.5656883593898</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>1.700417285731125</v>
+        <v>3.252793450253603</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L4" s="2" t="n">
         <v>0</v>
@@ -676,11 +676,11 @@
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.7516385136821135</v>
+        <v>0.9156809403365392</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -697,7 +697,7 @@
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>779.3412679407689</v>
+        <v>979.3412679407689</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>30.95</v>
@@ -711,10 +711,10 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>74.42042733993151</v>
+        <v>74.4204273837764</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>31.6714542571895</v>
+        <v>31.67145424523045</v>
       </c>
       <c r="J5" s="2" t="n">
         <v>2.43412679407689</v>
@@ -729,31 +729,31 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.5379825968161371</v>
+        <v>0.5379825967404444</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>4939</v>
+        <v>4542</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>亞電</t>
+          <t>科嶠</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>754.6757231839462</v>
+        <v>976.5970268783532</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>59.7</v>
+        <v>286</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,16 +764,16 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>80.23267848972962</v>
+        <v>65.26226355805557</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>29.34282681558172</v>
+        <v>39.07907768725583</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>1.967572318394614</v>
+        <v>3.659702687835325</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L6" s="2" t="n">
         <v>0</v>
@@ -782,31 +782,31 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>1.646497073814236</v>
+        <v>-0.4706831986191098</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>6112</v>
+        <v>6139</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>邁達特</t>
+          <t>亞翔</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>752.527934502536</v>
+        <v>965.8793153566556</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>50</v>
+        <v>808</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,49 +817,49 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>69.356925686118</v>
+        <v>60.50711624985009</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>22.56568845808417</v>
+        <v>28.46596714386722</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>3.252793450253603</v>
+        <v>1.587931535665568</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M7" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.915680940098046</v>
+        <v>0.1252023687980141</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>4958</v>
+        <v>5228</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>鈺鎧</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>752.234077676581</v>
+        <v>957.0041728573112</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>504</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,16 +870,16 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>59.45246548931983</v>
+        <v>77.71978076942094</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>41.57035761114419</v>
+        <v>48.81271720458227</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.2234077676581008</v>
+        <v>1.700417285731125</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" s="2" t="n">
         <v>0</v>
@@ -888,31 +888,31 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>-5.346137276519258</v>
+        <v>0.751638513720267</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>5493</v>
+        <v>4939</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>三聯</t>
+          <t>亞電</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>745.259324739615</v>
+        <v>954.6757231839462</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>93.09999999999999</v>
+        <v>59.7</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,16 +923,16 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>55.2052753690345</v>
+        <v>80.23267849551081</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>27.41010374967266</v>
+        <v>29.34282677309231</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>1.025932473961495</v>
+        <v>1.967572318394614</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" s="2" t="n">
         <v>0</v>
@@ -941,31 +941,31 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>-0.2573317424602259</v>
+        <v>1.64649707388102</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>6139</v>
+        <v>4938</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>亞翔</t>
+          <t>和碩</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>730.8793153566556</v>
+        <v>935.878651713878</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>808</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,49 +976,49 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>60.50711623936196</v>
+        <v>77.09220247220566</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>28.46596726156292</v>
+        <v>31.9633598508062</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>1.587931535665568</v>
+        <v>1.587865171387801</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M10" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.125202367653145</v>
+        <v>1.888730410473081</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>5351</v>
+        <v>5309</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>鈺創</t>
+          <t>系統電</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>718.649465078461</v>
+        <v>935.4962990413504</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>86.2</v>
+        <v>74.3</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,49 +1029,49 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>56.45582389782135</v>
+        <v>58.84310348437449</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>22.14318353090025</v>
+        <v>31.6058373253665</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>1.8649465078461</v>
+        <v>1.549629904135054</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M11" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>0.1703893428001208</v>
+        <v>0.9057158448717296</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>4972</v>
+        <v>5285</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>湯石照明</t>
+          <t>界霖</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>706.3105963891418</v>
+        <v>893.469564700338</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>16.95</v>
+        <v>91.8</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,49 +1082,49 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>68.54082274113203</v>
+        <v>69.48901839984833</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>37.51830778958959</v>
+        <v>58.35109848248747</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.6310596389141793</v>
+        <v>1.346956470033793</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M12" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>0.0820858769233296</v>
+        <v>0.3584073952366893</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>5285</v>
+        <v>5493</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>界霖</t>
+          <t>三聯</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>683.469564700338</v>
+        <v>885.259324739615</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>91.8</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,16 +1135,16 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>69.48901838178097</v>
+        <v>55.20527543223884</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>58.35109850613024</v>
+        <v>27.41010365881232</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>1.346956470033793</v>
+        <v>1.025932473961495</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" s="2" t="n">
         <v>0</v>
@@ -1153,31 +1153,31 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>0.3584073951508308</v>
+        <v>-0.2573317424602259</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>5230</v>
+        <v>5353</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>雷笛克光學</t>
+          <t>台林</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>683.2284162297688</v>
+        <v>875.3434717065078</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>18.35</v>
+        <v>34.05</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,13 +1188,13 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>64.40306488268077</v>
+        <v>88.66824036798351</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>18.72597867703081</v>
+        <v>58.06395076062639</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>1.822841622976878</v>
+        <v>2.534347170650782</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>0.1569573452833766</v>
+        <v>0.7708339675854985</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>5464</v>
+        <v>5230</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>霖宏</t>
+          <t>雷笛克光學</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>682.3255801965329</v>
+        <v>853.2284162297688</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>67.59999999999999</v>
+        <v>18.35</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,16 +1241,16 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>57.16343528545936</v>
+        <v>64.40306492630181</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>55.68285836159487</v>
+        <v>18.72597872092029</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.7325580196532883</v>
+        <v>1.822841622976878</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>-1.595483521321222</v>
+        <v>0.1569573453406148</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>4760</v>
+        <v>4972</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>勤凱</t>
+          <t>湯石照明</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>680.2583625037953</v>
+        <v>846.3105963891418</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>411</v>
+        <v>16.95</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,13 +1294,13 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>63.02041410982835</v>
+        <v>68.54082291755806</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>38.95428566777183</v>
+        <v>37.51830810054548</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>1.025836250379533</v>
+        <v>0.6310596389141793</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>2.198833941869985</v>
+        <v>0.0820858769519464</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>5425</v>
+        <v>5484</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>台半</t>
+          <t>慧友</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>676.404833277115</v>
+        <v>843.5173616073586</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>101</v>
+        <v>57.9</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,16 +1347,16 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>61.99096528971113</v>
+        <v>71.37422977055533</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>45.47291456540572</v>
+        <v>44.39741962889718</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.6404833277114963</v>
+        <v>1.35173616073586</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L17" s="2" t="n">
         <v>0</v>
@@ -1365,31 +1365,31 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>-0.1199815787127533</v>
+        <v>1.213961170402525</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>4933</v>
+        <v>4904</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>友輝</t>
+          <t>遠傳</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>676.2144367380893</v>
+        <v>835.4335608576055</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>73.90000000000001</v>
+        <v>101.5</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,13 +1400,13 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>55.32370040239861</v>
+        <v>66.68706947812946</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>36.19873422181174</v>
+        <v>20.98052451101489</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.6214436738089286</v>
+        <v>1.043356085760543</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>-0.1317124925538619</v>
+        <v>0.6831150930467724</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>4906</v>
+        <v>5452</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>正文</t>
+          <t>佶優</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>675.7551976263517</v>
+        <v>829.6547221046632</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>47.95</v>
+        <v>35.6</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,13 +1453,13 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>60.91611069090227</v>
+        <v>57.73135456030525</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>37.5520752313713</v>
+        <v>8.963064090158484</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.5755197626351664</v>
+        <v>2.465472210466313</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>0.5764419202594895</v>
+        <v>0.3027658685125162</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>5353</v>
+        <v>4973</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>台林</t>
+          <t>廣穎</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>675.3434717065078</v>
+        <v>818.8613786514541</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>34.05</v>
+        <v>171.5</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,16 +1506,16 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>88.66824036212718</v>
+        <v>78.6070470600304</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>58.06395088118398</v>
+        <v>48.72950191547866</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>2.534347170650782</v>
+        <v>0.3861378651454021</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>0.7708339674424038</v>
+        <v>3.93255755188175</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>5474</v>
+        <v>6155</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>聰泰</t>
+          <t>鈞寶</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>675.1869775054952</v>
+        <v>808.7682165385991</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>175.5</v>
+        <v>79.3</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,16 +1559,16 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>55.23559808277678</v>
+        <v>74.2955251206171</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>36.60038594729227</v>
+        <v>34.4358552376212</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.5186977505495161</v>
+        <v>1.376821653859902</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>-0.0264438290213879</v>
+        <v>1.78841123151708</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>5299</v>
+        <v>5426</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>杰力</t>
+          <t>振發</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>673.2765128551963</v>
+        <v>805</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>110</v>
+        <v>29.95</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,16 +1612,16 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>56.76517926948512</v>
+        <v>89.36325717730594</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>50.26402384878206</v>
+        <v>32.96227304058519</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.3276512855196308</v>
+        <v>10.70081994619837</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>-1.145316216877601</v>
+        <v>1.199497666625238</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>4938</v>
+        <v>6115</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>和碩</t>
+          <t>鎰勝</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>670.8409139905358</v>
+        <v>804.9636659091201</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>96.90000000000001</v>
+        <v>49.4</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,13 +1665,13 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>77.09220246175182</v>
+        <v>70.02960350581998</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>31.96335977809881</v>
+        <v>20.07043972019813</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>1.584091399053581</v>
+        <v>2.496366590912013</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>1.888730410492176</v>
+        <v>0.2789774981852383</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>5309</v>
+        <v>5269</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>系統電</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>670.4962990413505</v>
+        <v>800.155192710837</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>74.3</v>
+        <v>1525</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,13 +1718,13 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>58.8431034761776</v>
+        <v>57.63882297813966</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>31.60583738965979</v>
+        <v>31.24205605368392</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>1.549629904135054</v>
+        <v>0.515519271083702</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>0.9057158445283062</v>
+        <v>1.631866439910141</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>5536</v>
+        <v>5490</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>聖暉*</t>
+          <t>同亨</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>667.0349659983218</v>
+        <v>764.0475910067388</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>1130</v>
+        <v>29.15</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,16 +1771,16 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>67.12442364733243</v>
+        <v>54.49974006752439</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>31.0235273620861</v>
+        <v>35.64715496002127</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>1.203496599832183</v>
+        <v>0.904759100673882</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>8.464584055139355</v>
+        <v>0.009877322721213199</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>6115</v>
+        <v>6120</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>鎰勝</t>
+          <t>達運</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>664.9636659091201</v>
+        <v>759.2757438777396</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>49.4</v>
+        <v>15.3</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,16 +1824,16 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>70.02960332831256</v>
+        <v>60.13562947568283</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>20.07043960687983</v>
+        <v>22.47183900914335</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>2.496366590912013</v>
+        <v>0.9275743877739626</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>0.2789774982806295</v>
+        <v>0.2257365233817888</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>6141</v>
+        <v>4931</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>柏承</t>
+          <t>新盛力</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>660.6030534316155</v>
+        <v>759.1219954316509</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>38.5</v>
+        <v>242.5</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,13 +1877,13 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>55.93362159914816</v>
+        <v>65.03491297717329</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>28.22672550663404</v>
+        <v>46.71322720070297</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.5603053431615549</v>
+        <v>0.9121995431650888</v>
       </c>
       <c r="K27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>0.0341659009434711</v>
+        <v>3.263460256725516</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>5269</v>
+        <v>4545</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>銘鈺</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>660.155192710837</v>
+        <v>758.9676371287371</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>1525</v>
+        <v>40.1</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,16 +1930,16 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>57.63882307411038</v>
+        <v>68.64712496106765</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>31.24205582258853</v>
+        <v>46.86152157134515</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.515519271083702</v>
+        <v>0.8967637128737095</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>1.631866413199006</v>
+        <v>0.828988025507301</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>4923</v>
+        <v>4958</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>力士</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>654.5884476242023</v>
+        <v>752.234077676581</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>45.7</v>
+        <v>504</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,69 +1983,69 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>59.59638951837545</v>
+        <v>59.45246548756835</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>23.23115256099236</v>
+        <v>41.57035753742574</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.958844762420236</v>
+        <v>0.2234077676581008</v>
       </c>
       <c r="K29" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L29" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M29" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>0.1548077460951789</v>
+        <v>-5.346137276347534</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>4987</v>
+        <v>4995</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>科誠</t>
+          <t>晶達</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>647.5086491134235</v>
+        <v>744.0908657997867</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>81.59999999999999</v>
+        <v>46.15</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G30" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>55.06266588186581</v>
+        <v>54.20774742921742</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>23.90739774097927</v>
+        <v>32.08881739426668</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.750864911342356</v>
+        <v>0.4090865799786635</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>-0.0408812921681572</v>
+        <v>-0.1521659520361371</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>5484</v>
+        <v>5489</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>慧友</t>
+          <t>彩富</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>643.5173616073586</v>
+        <v>743.6697377191505</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>57.9</v>
+        <v>40.45</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,13 +2089,13 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>71.37422973275133</v>
+        <v>58.8674620606626</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>44.39741967921686</v>
+        <v>42.84837516421693</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>1.35173616073586</v>
+        <v>4.866973771915052</v>
       </c>
       <c r="K31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>1.213961170268963</v>
+        <v>0.0915123263291725</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>5452</v>
+        <v>4916</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>佶優</t>
+          <t>事欣科</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>639.6547221046632</v>
+        <v>742.5287227140955</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>35.6</v>
+        <v>120</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,16 +2142,16 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>57.73135455098357</v>
+        <v>75.94256565611067</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>8.963063954827355</v>
+        <v>49.10853495183739</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>2.465472210466313</v>
+        <v>0.2528722714095519</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>0.3027658683885008</v>
+        <v>2.39609817713646</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>4729</v>
+        <v>6116</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>熒茂</t>
+          <t>彩晶</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>620.5997636133793</v>
+        <v>741.1662578134167</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>24.3</v>
+        <v>18.45</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,16 +2195,16 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>54.12471160360538</v>
+        <v>66.39955129706681</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>50.26066848074562</v>
+        <v>54.2229123959189</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>1.059976361337937</v>
+        <v>0.1166257813416661</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>0.0704517236534116</v>
+        <v>0.7283929930959303</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>4931</v>
+        <v>5434</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>新盛力</t>
+          <t>崇越</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>619.1219954316509</v>
+        <v>734.0789100139789</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>242.5</v>
+        <v>458.5</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,49 +2248,49 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>65.03491295268221</v>
+        <v>58.69003600399597</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>46.71322726700521</v>
+        <v>30.60180403429602</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.9121995431650888</v>
+        <v>1.407891001397886</v>
       </c>
       <c r="K34" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L34" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M34" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>3.263460256725516</v>
+        <v>0.2372673939433056</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, invest_trust_buy_2d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>4545</v>
+        <v>6104</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>銘鈺</t>
+          <t>創惟</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>618.9676371287371</v>
+        <v>730.1515633991005</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>40.1</v>
+        <v>103</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,13 +2301,13 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>68.64712492032575</v>
+        <v>57.96109525321886</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>46.86152157901926</v>
+        <v>24.93600601137474</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.8967637128737095</v>
+        <v>1.015156339910049</v>
       </c>
       <c r="K35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>0.8289880254882176</v>
+        <v>0.2015440568727169</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>5321</v>
+        <v>5488</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>美而快</t>
+          <t>松普</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>617.0495631282161</v>
+        <v>726.6847808864213</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>45.55</v>
+        <v>13</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,16 +2354,16 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>58.13200364289335</v>
+        <v>63.33086853185064</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>59.1905286230351</v>
+        <v>44.75665284118946</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.7049563128216029</v>
+        <v>0.6684780886421314</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>0.7424673161024486</v>
+        <v>0.1751418963667033</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>5215</v>
+        <v>5388</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>科嘉-KY</t>
+          <t>中磊</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>614.4895380014401</v>
+        <v>725.7383796220114</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>48.4</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,16 +2407,16 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>64.49335488116745</v>
+        <v>59.58492088268827</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>57.751810158822</v>
+        <v>22.20111111220189</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.4489538001440144</v>
+        <v>0.5738379622011376</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>0.0686632663398363</v>
+        <v>0.690300731348954</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>5289</v>
+        <v>4967</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>宜鼎</t>
+          <t>十銓</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>609.5932831411375</v>
+        <v>722.455452227667</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>1755</v>
+        <v>279</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,13 +2460,13 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>56.1668418688404</v>
+        <v>51.41308894425601</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>37.68549279852349</v>
+        <v>33.11808191101772</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.959328314113751</v>
+        <v>1.245545222766704</v>
       </c>
       <c r="K38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>-13.81592788511784</v>
+        <v>0.5520905614440759</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>6155</v>
+        <v>4915</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>鈞寶</t>
+          <t>致伸</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>608.7682165385991</v>
+        <v>719.8797893774887</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>79.3</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,16 +2513,16 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>74.29552511644955</v>
+        <v>65.00948390149691</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>34.43585527464023</v>
+        <v>17.56207872812679</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>1.376821653859902</v>
+        <v>0.9879789377488648</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>1.788411231488467</v>
+        <v>0.7003401616992133</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>4967</v>
+        <v>5351</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>十銓</t>
+          <t>鈺創</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>607.455452227667</v>
+        <v>718.649465078461</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>279</v>
+        <v>86.2</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,13 +2566,13 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>51.41308893887058</v>
+        <v>56.45582390812194</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>33.11808190043045</v>
+        <v>22.14318346454473</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>1.245545222766704</v>
+        <v>1.8649465078461</v>
       </c>
       <c r="K40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>0.5520905611387787</v>
+        <v>0.1703893428669038</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>4585</v>
+        <v>5251</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>達明</t>
+          <t>天鉞電</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>605.9637593384974</v>
+        <v>687.7076063406793</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>346</v>
+        <v>31.15</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,13 +2619,13 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>52.12984974929154</v>
+        <v>60.44673694425603</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>22.78135658661828</v>
+        <v>35.72148727080397</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.5963759338497374</v>
+        <v>1.770760634067924</v>
       </c>
       <c r="K41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>-1.398782594208897</v>
+        <v>0.6927913134044144</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>5426</v>
+        <v>4919</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>振發</t>
+          <t>新唐</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>605</v>
+        <v>686.3782412281266</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>29.95</v>
+        <v>178</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,16 +2672,16 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>89.36325717503131</v>
+        <v>50.27404039381241</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>32.96227278995544</v>
+        <v>28.08267587268996</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>10.70081994619837</v>
+        <v>0.1378241228126606</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>1.199497666434445</v>
+        <v>-2.687006413154819</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>5489</v>
+        <v>5464</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>彩富</t>
+          <t>霖宏</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>603.6697377191505</v>
+        <v>682.3255801965329</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>40.45</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,13 +2725,13 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>58.86746166488154</v>
+        <v>57.16343527508305</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>42.84837512578693</v>
+        <v>55.68285835714999</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>4.866973771915052</v>
+        <v>0.7325580196532883</v>
       </c>
       <c r="K43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>0.0915123260334466</v>
+        <v>-1.595483521139965</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>4989</v>
+        <v>4760</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>榮科</t>
+          <t>勤凱</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>599.6292918337425</v>
+        <v>680.2583625037953</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>90.90000000000001</v>
+        <v>411</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,13 +2778,13 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>42.98241617705785</v>
+        <v>63.02041411461247</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>28.51356907091026</v>
+        <v>38.95428553489564</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.4629291833742489</v>
+        <v>1.025836250379533</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>-1.203525347793155</v>
+        <v>2.198833942308774</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>4952</v>
+        <v>5245</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>凌通</t>
+          <t>智晶</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>597.8231350418652</v>
+        <v>680.064406815178</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>49.4</v>
+        <v>27.85</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,16 +2831,16 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>46.37237355510883</v>
+        <v>59.44244399753584</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>28.94419184338751</v>
+        <v>37.41334981286735</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.2823135041865193</v>
+        <v>1.006440681517804</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>-0.6005292737502699</v>
+        <v>0.1780693855284905</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>4919</v>
+        <v>6103</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>新唐</t>
+          <t>合邦</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>596.3782412281266</v>
+        <v>678.3058893831751</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>178</v>
+        <v>39.2</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,13 +2884,13 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>50.27404037799779</v>
+        <v>52.48436274103906</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>28.08267586146182</v>
+        <v>10.41131392433229</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.1378241228126606</v>
+        <v>1.330588938317509</v>
       </c>
       <c r="K46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>-2.687006413212043</v>
+        <v>0.229425488346064</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive, stronger_than_market, obv_uptrend, williams_r_recovery, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>4904</v>
+        <v>5425</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>台半</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>590.3991557594651</v>
+        <v>676.404833277115</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>101.5</v>
+        <v>101</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,16 +2937,16 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>66.68706930695396</v>
+        <v>61.99096529665091</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>20.98052440407365</v>
+        <v>45.47291449328753</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>1.039915575946511</v>
+        <v>0.6404833277114963</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>0.6831150934665225</v>
+        <v>-0.1199815785314939</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>6104</v>
+        <v>4933</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>創惟</t>
+          <t>友輝</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>590.1515633991005</v>
+        <v>676.2144367380893</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>103</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,16 +2990,16 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>57.96109510125777</v>
+        <v>55.32370047501984</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>24.93600573257844</v>
+        <v>36.19873425599746</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>1.015156339910049</v>
+        <v>0.6214436738089286</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>0.2015440558233543</v>
+        <v>-0.1317124924966268</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>6120</v>
+        <v>4906</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>達運</t>
+          <t>正文</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>589.2757438777396</v>
+        <v>675.7551976263517</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>15.3</v>
+        <v>47.95</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,16 +3043,16 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>60.13562944354092</v>
+        <v>60.91611070420355</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>22.47183904584575</v>
+        <v>37.55207513677401</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.9275743877739626</v>
+        <v>0.5755197626351664</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>0.2257365233196613</v>
+        <v>0.5764419203739659</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>4979</v>
+        <v>5474</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>聰泰</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>587.3881091118673</v>
+        <v>675.1869775054952</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>596</v>
+        <v>175.5</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,13 +3096,13 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>48.953679881954</v>
+        <v>55.23559803685129</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>22.39698517882128</v>
+        <v>36.60038587205366</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.2388109111867299</v>
+        <v>0.5186977505495161</v>
       </c>
       <c r="K50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>-6.220060984085816</v>
+        <v>-0.0264438267318336</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>5388</v>
+        <v>6152</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>中磊</t>
+          <t>百一</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>585.7383796220114</v>
+        <v>674.957159908612</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>89.59999999999999</v>
+        <v>15.8</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,16 +3149,16 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>59.58492069844944</v>
+        <v>53.52694704481335</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>22.20111094173129</v>
+        <v>12.122784148556</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.5738379622011376</v>
+        <v>0.9957159908611982</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>0.6903007312917087</v>
+        <v>0.0964523277482837</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>4973</v>
+        <v>5299</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>廣穎</t>
+          <t>杰力</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>573.8613786514541</v>
+        <v>673.2765128551963</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>171.5</v>
+        <v>110</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,13 +3202,13 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>78.60704705857208</v>
+        <v>56.76517928686452</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>48.72950201245496</v>
+        <v>50.26402380274871</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.3861378651454021</v>
+        <v>0.3276512855196308</v>
       </c>
       <c r="K52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>3.932557551814991</v>
+        <v>-1.145316216572337</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>4916</v>
+        <v>4976</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>事欣科</t>
+          <t>佳凌</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>572.5287227140955</v>
+        <v>663.1331135224207</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>120</v>
+        <v>33.7</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,13 +3255,13 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>75.94256564354242</v>
+        <v>61.64549123753746</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>49.10853498185832</v>
+        <v>35.87215583221219</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.2528722714095519</v>
+        <v>1.813311352242068</v>
       </c>
       <c r="K53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>2.396098176888422</v>
+        <v>0.2309425755114768</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>6116</v>
+        <v>4979</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>彩晶</t>
+          <t>華星光</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>571.1662578134167</v>
+        <v>662.3881091118673</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>18.45</v>
+        <v>596</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,16 +3308,16 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>66.39955129643459</v>
+        <v>48.95367990066813</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>54.22291240271635</v>
+        <v>22.39698500702864</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.1166257813416661</v>
+        <v>0.2388109111867299</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>0.7283929930654023</v>
+        <v>-6.220060983608793</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>5490</v>
+        <v>6141</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>同亨</t>
+          <t>柏承</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>559.0475910067388</v>
+        <v>660.6030534316155</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>29.15</v>
+        <v>38.5</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,13 +3361,13 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>54.49974002592589</v>
+        <v>55.93362160032757</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>35.64715487524235</v>
+        <v>28.2267254917358</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.904759100673882</v>
+        <v>0.5603053431615549</v>
       </c>
       <c r="K55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>0.009877322673515499</v>
+        <v>0.0341659009892616</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>5488</v>
+        <v>4923</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>松普</t>
+          <t>力士</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>556.6847808864213</v>
+        <v>654.5884476242023</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>13</v>
+        <v>45.7</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,16 +3414,16 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>63.33086849696033</v>
+        <v>59.59638954018724</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>44.75665295198353</v>
+        <v>23.23115250584691</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.6684780886421314</v>
+        <v>0.958844762420236</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L56" s="2" t="n">
         <v>0</v>
@@ -3432,48 +3432,48 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>0.1751418963380837</v>
+        <v>0.1548077462859751</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>5236</v>
+        <v>4987</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>凌陽創新</t>
+          <t>科誠</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>549.1809137978018</v>
+        <v>647.5086491134235</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>164.5</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G57" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>44.75993543976147</v>
+        <v>55.0626655231763</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>38.50239318896357</v>
+        <v>23.90739732888225</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.4180913797801798</v>
+        <v>0.750864911342356</v>
       </c>
       <c r="K57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>-2.773016776251349</v>
+        <v>-0.0408812910631183</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>4974</v>
+        <v>4924</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>亞泰</t>
+          <t>欣厚-KY</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>545.2614232004942</v>
+        <v>646.3380222298449</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>77.2</v>
+        <v>12.75</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,13 +3520,13 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>59.13560742161686</v>
+        <v>62.87311574695726</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>29.74250271773357</v>
+        <v>32.87647461467009</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>1.026142320049409</v>
+        <v>0.1338022229844962</v>
       </c>
       <c r="K58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>0.1001334899792822</v>
+        <v>0.0772308931983913</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>4912</v>
+        <v>5356</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>聯德控股-KY</t>
+          <t>協益</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>545.007250239174</v>
+        <v>645.2389087483452</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>92.7</v>
+        <v>27.35</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,13 +3573,13 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>42.47372031078425</v>
+        <v>60.93947731603437</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>32.51251447383802</v>
+        <v>30.97473547644952</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.5007250239174041</v>
+        <v>1.023890874834527</v>
       </c>
       <c r="K59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>-1.982661352890872</v>
+        <v>0.0334249580412244</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>4935</v>
+        <v>5227</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>茂林-KY</t>
+          <t>立凱-KY</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>544.4469254061054</v>
+        <v>644.993349319546</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>41.1</v>
+        <v>25.2</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,13 +3626,13 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>65.98988357704468</v>
+        <v>57.87633657039034</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>26.57387546772764</v>
+        <v>24.88283282932765</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.9446925406105388</v>
+        <v>0.9993349319546052</v>
       </c>
       <c r="K60" s="2" t="n">
         <v>0</v>
@@ -3644,11 +3644,11 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>0.5132940085340796</v>
+        <v>0.06627019417847969</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -3665,7 +3665,7 @@
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>543.3157802780047</v>
+        <v>633.3157802780047</v>
       </c>
       <c r="E61" s="2" t="n">
         <v>30.4</v>
@@ -3679,16 +3679,16 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>49.79800025547548</v>
+        <v>49.7980002108292</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>34.24087377502927</v>
+        <v>34.24087375092987</v>
       </c>
       <c r="J61" s="2" t="n">
         <v>0.331578027800464</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>-0.1582115047177762</v>
+        <v>-0.1582115045556019</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>5245</v>
+        <v>4961</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>智晶</t>
+          <t>天鈺</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>540.064406815178</v>
+        <v>630.0545329530216</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>27.85</v>
+        <v>168.5</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,49 +3732,49 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>59.44244385048837</v>
+        <v>50.17021294563317</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>37.41334981286735</v>
+        <v>28.10022793378869</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>1.006440681517804</v>
+        <v>0.505453295302169</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L62" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M62" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>0.1780693855952673</v>
+        <v>-1.243518779447479</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, invest_trust_buy_2d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>4995</v>
+        <v>5465</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>晶達</t>
+          <t>富驊</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>539.0908657997866</v>
+        <v>629.0830951752405</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>46.15</v>
+        <v>27.15</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,16 +3785,16 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>54.20774739951383</v>
+        <v>58.49576887115163</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>32.08881746008824</v>
+        <v>32.79972359212154</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.4090865799786635</v>
+        <v>2.408309517524051</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>-0.1521659519407422</v>
+        <v>0.3015849701526136</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>6103</v>
+        <v>5392</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>合邦</t>
+          <t>能率</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>538.3058893831751</v>
+        <v>620.6035037110446</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>39.2</v>
+        <v>45.6</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,13 +3838,13 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>52.48436274549243</v>
+        <v>56.79353985921108</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>10.41131386694906</v>
+        <v>15.2999912462535</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>1.330588938317509</v>
+        <v>1.060350371104459</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>0.2294254882697486</v>
+        <v>0.2919494263594857</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, williams_r_recovery, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>5471</v>
+        <v>4729</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>松翰</t>
+          <t>熒茂</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>537.8923731389272</v>
+        <v>620.5997636133793</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>51.2</v>
+        <v>24.3</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,13 +3891,13 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>53.26893706124376</v>
+        <v>54.12471161827117</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>37.21944431331305</v>
+        <v>50.26066850633489</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.289237313892713</v>
+        <v>1.059976361337937</v>
       </c>
       <c r="K65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>-0.5199081579073273</v>
+        <v>0.0704517237488111</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>4961</v>
+        <v>5321</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>天鈺</t>
+          <t>美而快</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>535.0545329530216</v>
+        <v>617.0495631282161</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>168.5</v>
+        <v>45.55</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,13 +3944,13 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>50.17021290205713</v>
+        <v>58.13200364361313</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>28.10022763334331</v>
+        <v>59.19052872181195</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.505453295302169</v>
+        <v>0.7049563128216029</v>
       </c>
       <c r="K66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>-1.24351877992447</v>
+        <v>0.7424673161024486</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>5386</v>
+        <v>5215</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>青雲</t>
+          <t>科嘉-KY</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>534.0050894979113</v>
+        <v>614.4895380014401</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>511</v>
+        <v>48.4</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,16 +3997,16 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>54.15049655291136</v>
+        <v>64.49335488894408</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>32.24533218630584</v>
+        <v>57.75181011117481</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>1.400508949791123</v>
+        <v>0.4489538001440144</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>-4.043023051602432</v>
+        <v>0.0686632665115518</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>5356</v>
+        <v>5471</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>協益</t>
+          <t>松翰</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>530.2389087483452</v>
+        <v>612.8923731389272</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>27.35</v>
+        <v>51.2</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,16 +4050,16 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>60.93947730612006</v>
+        <v>53.26893709909129</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>30.97473597991789</v>
+        <v>37.21944438435715</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>1.023890874834527</v>
+        <v>0.289237313892713</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>0.0334249579458281</v>
+        <v>-0.5199081578596241</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>5227</v>
+        <v>5481</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>立凱-KY</t>
+          <t>新華</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>529.993349319546</v>
+        <v>611.8924952646456</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>25.2</v>
+        <v>18.7</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,13 +4103,13 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>57.87633639630555</v>
+        <v>36.4787038203511</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>24.88283268015375</v>
+        <v>21.62367699878499</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.9993349319546052</v>
+        <v>0.6892495264645627</v>
       </c>
       <c r="K69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>0.06627019417847969</v>
+        <v>0.0070039902165299</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>5274</v>
+        <v>5289</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>信驊</t>
+          <t>宜鼎</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>528.966337302562</v>
+        <v>609.5932831411375</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>17505</v>
+        <v>1755</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,13 +4156,13 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>52.89480904309068</v>
+        <v>56.16684187629488</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>30.12829955965615</v>
+        <v>37.68549281733466</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.8966337302562012</v>
+        <v>0.959328314113751</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>-113.2157566764686</v>
+        <v>-13.81592788569</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>5483</v>
+        <v>4585</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>中美晶</t>
+          <t>達明</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>527.6282369405797</v>
+        <v>605.9637593384974</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>152.5</v>
+        <v>346</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,13 +4209,13 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>51.07912083476619</v>
+        <v>52.12984991938343</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>28.50947973744982</v>
+        <v>22.78135660779907</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.7628236940579666</v>
+        <v>0.5963759338497374</v>
       </c>
       <c r="K71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>-0.5459833925856916</v>
+        <v>-1.398782597070861</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>4949</v>
+        <v>5438</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>有成精密</t>
+          <t>東友</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>524.3322853383954</v>
+        <v>601.5351349448617</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>93.90000000000001</v>
+        <v>19.8</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,16 +4262,16 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>48.89663683371509</v>
+        <v>57.83938961924657</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>30.03923195580333</v>
+        <v>27.53167342622957</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.4332285338395459</v>
+        <v>0.6535134944861752</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>-0.6748386929799866</v>
+        <v>0.1264224225545072</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>5434</v>
+        <v>4989</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>崇越</t>
+          <t>榮科</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>522.875085844906</v>
+        <v>599.6292918337425</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>458.5</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,16 +4315,16 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>58.69003597623621</v>
+        <v>42.98241618311383</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>30.6018041574224</v>
+        <v>28.51356906191209</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>1.287508584490603</v>
+        <v>0.4629291833742489</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>0.2372673942294625</v>
+        <v>-1.203525347745463</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>4749</v>
+        <v>4949</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>新應材</t>
+          <t>有成精密</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>518.899778992258</v>
+        <v>599.3322853383954</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>1015</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,13 +4368,13 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>45.55937478106945</v>
+        <v>48.89663685911398</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>21.5692134642774</v>
+        <v>30.03923197841537</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.3899778992258059</v>
+        <v>0.4332285338395459</v>
       </c>
       <c r="K74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>-14.292310806674</v>
+        <v>-0.6748386927319618</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>5243</v>
+        <v>4952</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>乙盛-KY</t>
+          <t>凌通</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>510.5374995008096</v>
+        <v>597.8231350418652</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>112.5</v>
+        <v>49.4</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,13 +4421,13 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>47.46004216503344</v>
+        <v>46.37237363008716</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>24.98942168692315</v>
+        <v>28.94419194963828</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.5537499500809639</v>
+        <v>0.2823135041865193</v>
       </c>
       <c r="K75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>-0.7927352754158612</v>
+        <v>-0.6005292737788868</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>4991</v>
+        <v>5203</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>環宇-KY</t>
+          <t>訊連</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>507.4059082672628</v>
+        <v>592.3112492221271</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>654</v>
+        <v>71.8</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,13 +4474,13 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>45.70343708302718</v>
+        <v>72.90997411290303</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>18.93815926580359</v>
+        <v>24.49132414961393</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>1.240590826726279</v>
+        <v>1.231124922212708</v>
       </c>
       <c r="K76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>-17.83398732121714</v>
+        <v>0.8403262050605039</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>5392</v>
+        <v>5344</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>能率</t>
+          <t>立衛</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>505.6035037110446</v>
+        <v>587.6136113578608</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>45.6</v>
+        <v>16.05</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,16 +4527,16 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>56.79353981575849</v>
+        <v>50.61913301877516</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>15.29999132291082</v>
+        <v>24.20480372563725</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>1.060350371104459</v>
+        <v>0.7613611357860781</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>0.2919494262736228</v>
+        <v>0.0159421972883386</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>4915</v>
+        <v>6133</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>致伸</t>
+          <t>金橋</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>504.8797893774886</v>
+        <v>587.399954414473</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>77.40000000000001</v>
+        <v>24.15</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,13 +4580,13 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>65.00948379814353</v>
+        <v>57.53415146956515</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>17.56207860622733</v>
+        <v>15.37256881244763</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.9879789377488648</v>
+        <v>3.739995441447296</v>
       </c>
       <c r="K78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>0.7003401616801381</v>
+        <v>0.1516142624911243</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>4956</v>
+        <v>5225</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>光鋐</t>
+          <t>東科-KY</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>504.1904978252597</v>
+        <v>584.8209673099229</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>42.85</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,13 +4633,13 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>44.64849260801592</v>
+        <v>52.18076814410029</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>20.59343733548092</v>
+        <v>42.54640943986082</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.4190497825259663</v>
+        <v>1.98209673099229</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>0</v>
@@ -4651,51 +4651,51 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>-0.5361100851547053</v>
+        <v>1.106278585913872</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>4945</v>
+        <v>6153</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>陞達科技</t>
+          <t>嘉聯益</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>499.2651276632713</v>
+        <v>563.5348389940973</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>76.09999999999999</v>
+        <v>18.5</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G80" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>54.15717852531349</v>
+        <v>51.68659349089192</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>12.92781963699664</v>
+        <v>13.84834952734063</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.4265127663271301</v>
+        <v>0.85348389940973</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>0.5436131521152987</v>
+        <v>0.0296631669189404</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>4976</v>
+        <v>4577</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>佳凌</t>
+          <t>達航科技</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>493.1331135224207</v>
+        <v>560.6465249486919</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>33.7</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,16 +4739,16 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>61.64549119061017</v>
+        <v>30.56980013623416</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>35.87215588418451</v>
+        <v>26.24332244068361</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>1.813311352242068</v>
+        <v>0.564652494869194</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>0.230942575377919</v>
+        <v>-3.667517397101689</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, kd_golden_cross, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>5465</v>
+        <v>5223</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>富驊</t>
+          <t>安力-KY</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>489.0830951752405</v>
+        <v>553.1792677014537</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>27.15</v>
+        <v>26.35</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,13 +4792,13 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>58.49576882879523</v>
+        <v>59.8009311790471</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>32.79972337140506</v>
+        <v>21.1484092191965</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>2.408309517524051</v>
+        <v>0.3179267701453629</v>
       </c>
       <c r="K82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>0.3015849700285981</v>
+        <v>0.2546979627705723</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>5251</v>
+        <v>5236</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>天鉞電</t>
+          <t>凌陽創新</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>487.7076063406793</v>
+        <v>549.1809137978018</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>31.15</v>
+        <v>164.5</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,16 +4845,16 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>60.44673692647535</v>
+        <v>44.75993547558242</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>35.72148702909082</v>
+        <v>38.50239319762941</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>1.770760634067924</v>
+        <v>0.4180913797801798</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>0.6927913127461691</v>
+        <v>-2.77301677577435</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>4924</v>
+        <v>4974</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>欣厚-KY</t>
+          <t>亞泰</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>476.338022229845</v>
+        <v>545.2614232004942</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>12.75</v>
+        <v>77.2</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,16 +4898,16 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>62.87311563638318</v>
+        <v>59.13560756073964</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>32.87647471994695</v>
+        <v>29.74250294721534</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.1338022229844962</v>
+        <v>1.026142320049409</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>0.0772308932556294</v>
+        <v>0.1001334901700823</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>4908</v>
+        <v>4912</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>前鼎</t>
+          <t>聯德控股-KY</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>472.7079895658235</v>
+        <v>545.007250239174</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>226.5</v>
+        <v>92.7</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,16 +4951,16 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>49.0793744815797</v>
+        <v>42.47372039516929</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>40.55878974796676</v>
+        <v>32.51251437971525</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.7707989565823563</v>
+        <v>0.5007250239174041</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>-6.674273744059398</v>
+        <v>-1.982661352833626</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>5205</v>
+        <v>4935</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>中茂</t>
+          <t>茂林-KY</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>472.3850716957859</v>
+        <v>544.4469254061054</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>22.75</v>
+        <v>41.1</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,16 +5004,16 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>48.67112700652707</v>
+        <v>65.98988367287535</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>20.66657664396343</v>
+        <v>26.57387555098687</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>1.238507169578589</v>
+        <v>0.9446925406105388</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>0.0969563625232949</v>
+        <v>0.5132940085054623</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>4951</v>
+        <v>4960</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>精拓科</t>
+          <t>誠美材</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>471.9527729320275</v>
+        <v>539.7559306138988</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>113</v>
+        <v>32.6</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,16 +5057,16 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>45.98170909660102</v>
+        <v>46.10914813239113</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>36.03532045407513</v>
+        <v>16.77603780161221</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.6952772932027549</v>
+        <v>0.4755930613898853</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>-3.2762526842658</v>
+        <v>-0.4511473100084945</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>5481</v>
+        <v>5386</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>新華</t>
+          <t>青雲</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>471.8924952646456</v>
+        <v>534.0050894979113</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>18.7</v>
+        <v>511</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,13 +5110,13 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>36.47897147574728</v>
+        <v>54.15049655311448</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>21.62369405404131</v>
+        <v>32.24533214833866</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.6892495264645627</v>
+        <v>1.400508949791123</v>
       </c>
       <c r="K88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>0.0070037124339893</v>
+        <v>-4.043023051220842</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>4966</v>
+        <v>5274</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>譜瑞-KY</t>
+          <t>信驊</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>471.6844918021157</v>
+        <v>528.966337302562</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>736</v>
+        <v>17505</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,13 +5163,13 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>48.58824285355688</v>
+        <v>52.89480904224978</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>35.409107425557</v>
+        <v>30.12829948456572</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.668449180211567</v>
+        <v>0.8966337302562012</v>
       </c>
       <c r="K89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>-15.15752250028198</v>
+        <v>-113.2157566612059</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>5220</v>
+        <v>5483</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>萬達光電</t>
+          <t>中美晶</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>467.9610476300239</v>
+        <v>527.6282369405797</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>23</v>
+        <v>152.5</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,16 +5216,16 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>58.61306912474622</v>
+        <v>51.07912086178435</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>44.13686676552621</v>
+        <v>28.50947969022789</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.2961047630023926</v>
+        <v>0.7628236940579666</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>-0.0782748203976094</v>
+        <v>-0.5459833927764839</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>5438</v>
+        <v>4749</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>東友</t>
+          <t>新應材</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>461.5351349448617</v>
+        <v>518.899778992258</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>19.8</v>
+        <v>1015</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,13 +5269,13 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>57.83938948703835</v>
+        <v>45.55937483624653</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>27.53167336696764</v>
+        <v>21.56921341100036</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.6535134944861752</v>
+        <v>0.3899778992258059</v>
       </c>
       <c r="K91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>0.1264224224877267</v>
+        <v>-14.29231080562454</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>6108</v>
+        <v>5371</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>競國</t>
+          <t>中光電</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>450.4500051929379</v>
+        <v>514.2943422095159</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>19.6</v>
+        <v>73.5</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,49 +5322,49 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>51.77256949541536</v>
+        <v>51.78802175653312</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>17.83071935892361</v>
+        <v>14.37701189927148</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.5450005192937833</v>
+        <v>0.9294342209515928</v>
       </c>
       <c r="K92" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L92" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M92" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>-0.08684917804308161</v>
+        <v>0.5617420884812079</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>5344</v>
+        <v>6128</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>立衛</t>
+          <t>上福</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>447.6136113578608</v>
+        <v>512.3899892181253</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>16.05</v>
+        <v>20.8</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,13 +5375,13 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>50.61913294125352</v>
+        <v>59.70506247974149</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>24.20480373548565</v>
+        <v>30.29417346336045</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.7613611357860781</v>
+        <v>0.7389989218125296</v>
       </c>
       <c r="K93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>0.0159421972597203</v>
+        <v>0.2903485147341266</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>6133</v>
+        <v>5243</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>金橋</t>
+          <t>乙盛-KY</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>447.399954414473</v>
+        <v>510.5374995008096</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>24.15</v>
+        <v>112.5</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,16 +5428,16 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>57.534151447566</v>
+        <v>47.46004217369627</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>15.37256882387016</v>
+        <v>24.98942150920961</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>3.739995441447296</v>
+        <v>0.5537499500809639</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>0.1516142623861901</v>
+        <v>-0.7927352752250689</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>4927</v>
+        <v>4991</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>泰鼎-KY</t>
+          <t>環宇-KY</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>445.5976488911754</v>
+        <v>507.4059082672628</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>51.8</v>
+        <v>654</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,16 +5481,16 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>46.74529357622894</v>
+        <v>45.70343708522122</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>26.29531886677199</v>
+        <v>18.93815921028121</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.5597648891175415</v>
+        <v>1.240590826726279</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>-0.6184119304764142</v>
+        <v>-17.83398731986249</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>5443</v>
+        <v>4956</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>均豪</t>
+          <t>光鋐</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>445.0671802777772</v>
+        <v>504.1904978252597</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>115</v>
+        <v>42.85</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,16 +5534,16 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>43.22254591043086</v>
+        <v>44.64849262818501</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>12.46675811920913</v>
+        <v>20.59343738009397</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.5067180277777169</v>
+        <v>0.4190497825259663</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>-1.521850637725119</v>
+        <v>-0.5361100850211438</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>6152</v>
+        <v>4942</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>百一</t>
+          <t>嘉彰</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>444.957159908612</v>
+        <v>500.0256163651415</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>15.8</v>
+        <v>38.2</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,16 +5587,16 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>53.5269470664074</v>
+        <v>53.84938784896165</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>12.12278419539694</v>
+        <v>24.42974669302039</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.9957159908611982</v>
+        <v>0.5025616365141437</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L97" s="2" t="n">
         <v>0</v>
@@ -5605,51 +5605,51 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>0.0964523276433471</v>
+        <v>0.1251410975433573</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>5439</v>
+        <v>4945</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>高技</t>
+          <t>陞達科技</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>442.1002337345221</v>
+        <v>499.2651276632713</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>364.5</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="G98" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>45.14146466058845</v>
+        <v>54.21433334525088</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>21.23883273933699</v>
+        <v>12.90661095514172</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.7100233734522138</v>
+        <v>0.4265127663271301</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>-3.583712201080364</v>
+        <v>0.5437747586704251</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>4960</v>
+        <v>5475</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>誠美材</t>
+          <t>德宏</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>424.7559306138989</v>
+        <v>491.8026296380325</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>32.6</v>
+        <v>280.5</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,16 +5693,16 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>46.10914812079773</v>
+        <v>44.59958558871013</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>16.77603792173943</v>
+        <v>17.1251325726188</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.4755930613898853</v>
+        <v>0.6802629638032447</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>-0.4511473100466557</v>
+        <v>-0.6965559834793513</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>6153</v>
+        <v>4588</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>嘉聯益</t>
+          <t>玖鼎電力</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>423.5348389940973</v>
+        <v>488.896943679327</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>18.5</v>
+        <v>60.2</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,16 +5746,16 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>51.68659347256511</v>
+        <v>56.28309724552281</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>13.84834968122142</v>
+        <v>23.43385181167569</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.85348389940973</v>
+        <v>1.389694367932697</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>0.0296631668617032</v>
+        <v>0.8621045636164386</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>5291</v>
+        <v>4999</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>邑昇</t>
+          <t>鑫禾</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>423.044147350913</v>
+        <v>484.9238390239365</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>67.8</v>
+        <v>21.65</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,13 +5799,13 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>45.93413769250328</v>
+        <v>57.91223441947056</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>18.21175317075947</v>
+        <v>23.26497972854784</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.3044147350912939</v>
+        <v>0.992383902393654</v>
       </c>
       <c r="K101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>-0.9563780408047662</v>
+        <v>0.3195243682897631</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>6117</v>
+        <v>4905</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>迎廣</t>
+          <t>台聯電</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>422.0389465904996</v>
+        <v>476.2470876006184</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>83</v>
+        <v>81.2</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,13 +5852,13 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>48.05883435797087</v>
+        <v>50.35489310260822</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>17.8885214255494</v>
+        <v>10.12089682824396</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.7038946590499602</v>
+        <v>0.6247087600618408</v>
       </c>
       <c r="K102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>-0.2934922623199212</v>
+        <v>0.335837422907159</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>4577</v>
+        <v>4908</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>達航科技</t>
+          <t>前鼎</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>395.6465249486919</v>
+        <v>472.7079895658235</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>97.59999999999999</v>
+        <v>226.5</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,16 +5905,16 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>30.56980011475292</v>
+        <v>49.07937449237015</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>26.24332240193898</v>
+        <v>40.5587896725355</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.564652494869194</v>
+        <v>0.7707989565823563</v>
       </c>
       <c r="K103" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>-3.667517397101689</v>
+        <v>-6.674273743696897</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>5203</v>
+        <v>4951</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>訊連</t>
+          <t>精拓科</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>392.3112492221271</v>
+        <v>471.9527729320275</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>71.8</v>
+        <v>113</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,13 +5958,13 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>72.90997370420628</v>
+        <v>45.98170912173967</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>24.49132399577359</v>
+        <v>36.0353203822535</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>1.231124922212708</v>
+        <v>0.6952772932027549</v>
       </c>
       <c r="K104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>0.8403262056138172</v>
+        <v>-3.276252684303964</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>4942</v>
+        <v>4966</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>嘉彰</t>
+          <t>譜瑞-KY</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>385.0256163651415</v>
+        <v>471.6844918021157</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>38.2</v>
+        <v>736</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,16 +6011,16 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>53.84938771546423</v>
+        <v>48.58824284421092</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>24.42974669302039</v>
+        <v>35.40910748902729</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.5025616365141437</v>
+        <v>0.668449180211567</v>
       </c>
       <c r="K105" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>0.1251410976196772</v>
+        <v>-15.15752249665698</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>5223</v>
+        <v>5220</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>安力-KY</t>
+          <t>萬達光電</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>383.1792677014536</v>
+        <v>467.9610476300239</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>26.35</v>
+        <v>23</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,13 +6064,13 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>59.80093105281201</v>
+        <v>58.61306915807167</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>21.1484092191965</v>
+        <v>44.13686662957507</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.3179267701453629</v>
+        <v>0.2961047630023926</v>
       </c>
       <c r="K106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>0.2546979627514946</v>
+        <v>-0.0782748204357661</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>5234</v>
+        <v>5287</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>達興材料</t>
+          <t>數字</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>370.2088109237973</v>
+        <v>460.7913799388069</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>403.5</v>
+        <v>149.5</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,13 +6117,13 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>46.50058993470915</v>
+        <v>45.74115960199059</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>13.70677159506688</v>
+        <v>26.18469289324905</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>1.020881092379727</v>
+        <v>1.079137993880684</v>
       </c>
       <c r="K107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>-3.284237035460662</v>
+        <v>0.2503932326101736</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>5225</v>
+        <v>5345</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>東科-KY</t>
+          <t>天揚</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>369.8209673099229</v>
+        <v>456.951836457674</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>74.90000000000001</v>
+        <v>24.2</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,13 +6170,13 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>52.18076810056559</v>
+        <v>54.46921357070771</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>42.54640918366362</v>
+        <v>5.107371802121706</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>1.98209673099229</v>
+        <v>1.195183645767399</v>
       </c>
       <c r="K108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>1.106278585131611</v>
+        <v>0.578585129541517</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, market_above_ma60, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>5498</v>
+        <v>5348</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>凱崴</t>
+          <t>正能量智能</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>369.2950113588209</v>
+        <v>453.0453451898773</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>61.8</v>
+        <v>15.45</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,13 +6223,13 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>41.05204346796462</v>
+        <v>52.37019700961988</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>14.29748162011198</v>
+        <v>16.69749412138674</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.4295011358820925</v>
+        <v>0.3045345189877272</v>
       </c>
       <c r="K109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>-0.8220805775978</v>
+        <v>0.332747769271587</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>6136</v>
+        <v>6108</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>富爾特</t>
+          <t>競國</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>367.1025912190054</v>
+        <v>450.4500051929379</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>25.85</v>
+        <v>19.6</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,16 +6276,16 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>52.16877592917244</v>
+        <v>51.77256952281762</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>13.65353666993598</v>
+        <v>17.83071935009167</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>1.210259121900539</v>
+        <v>0.5450005192937833</v>
       </c>
       <c r="K110" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>0.079432358423753</v>
+        <v>-0.0868491780144625</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>4905</v>
+        <v>4927</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>台聯電</t>
+          <t>泰鼎-KY</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>361.2470876006184</v>
+        <v>445.5976488911754</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>81.2</v>
+        <v>51.8</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,13 +6329,13 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>50.35489314507829</v>
+        <v>46.74529360889085</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>10.12089680411982</v>
+        <v>26.2953187569307</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.6247087600618408</v>
+        <v>0.5597648891175415</v>
       </c>
       <c r="K111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>0.3358374225446532</v>
+        <v>-0.6184119304096418</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>4971</v>
+        <v>5347</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>IET-KY</t>
+          <t>世界</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>361.2039560290591</v>
+        <v>445.407168950214</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>670</v>
+        <v>161.5</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,16 +6382,16 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>44.33791295179424</v>
+        <v>50.23483688467942</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>13.24000975632327</v>
+        <v>16.95167877260607</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>1.12039560290591</v>
+        <v>0.5407168950214005</v>
       </c>
       <c r="K112" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L112" s="2" t="n">
         <v>0</v>
@@ -6400,31 +6400,31 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>-10.05126555004212</v>
+        <v>-1.665768302220773</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>5347</v>
+        <v>5443</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>世界</t>
+          <t>均豪</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>355.407168950214</v>
+        <v>445.0671802777772</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>161.5</v>
+        <v>115</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,13 +6435,13 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>50.2348368957062</v>
+        <v>43.22254591334501</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>16.95167871977037</v>
+        <v>12.46675796580983</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.5407168950214005</v>
+        <v>0.5067180277777169</v>
       </c>
       <c r="K113" s="2" t="n">
         <v>0</v>
@@ -6453,31 +6453,31 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>-1.665768302621441</v>
+        <v>-1.521850637019179</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>5475</v>
+        <v>5439</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>德宏</t>
+          <t>高技</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>351.8026296380324</v>
+        <v>442.1002337345221</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>280.5</v>
+        <v>364.5</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,16 +6488,16 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>44.59958558759472</v>
+        <v>45.14146469342801</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>17.1251325726758</v>
+        <v>21.23883270767181</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.6802629638032447</v>
+        <v>0.7100233734522138</v>
       </c>
       <c r="K114" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L114" s="2" t="n">
         <v>0</v>
@@ -6506,31 +6506,31 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>-0.6965559835175164</v>
+        <v>-3.583712201366529</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>5287</v>
+        <v>5450</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>數字</t>
+          <t>寶聯通</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>345.7913799388069</v>
+        <v>436.8153507953567</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>149.5</v>
+        <v>13.3</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,13 +6541,13 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>45.74115946632274</v>
+        <v>56.2203479161564</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>26.18469289324904</v>
+        <v>17.98291782399587</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>1.079137993880684</v>
+        <v>0.1815350795356678</v>
       </c>
       <c r="K115" s="2" t="n">
         <v>0</v>
@@ -6559,31 +6559,31 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>0.2503932327055902</v>
+        <v>0.1216290314385628</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>4977</v>
+        <v>5487</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>眾達-KY</t>
+          <t>通泰</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>344.600939549523</v>
+        <v>434.023534638285</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>200.5</v>
+        <v>27.65</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -6594,13 +6594,13 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>47.24904909716647</v>
+        <v>49.6159523868152</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>14.87835480067888</v>
+        <v>12.70970801338853</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>0.460093954952304</v>
+        <v>0.4023534638284962</v>
       </c>
       <c r="K116" s="2" t="n">
         <v>0</v>
@@ -6612,31 +6612,31 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>-2.099727984114553</v>
+        <v>0.0328472334694756</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>6128</v>
+        <v>5291</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>上福</t>
+          <t>邑昇</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
         <v/>
       </c>
       <c r="D117" s="2" t="n">
-        <v>342.3899892181253</v>
+        <v>423.044147350913</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>20.8</v>
+        <v>67.8</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -6647,13 +6647,13 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>59.70506252005016</v>
+        <v>45.93413769509662</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>30.29417277927794</v>
+        <v>18.21175323727635</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>0.7389989218125296</v>
+        <v>0.3044147350912939</v>
       </c>
       <c r="K117" s="2" t="n">
         <v>0</v>
@@ -6665,31 +6665,31 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>0.2903485145814902</v>
+        <v>-0.9563780406139626</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>5348</v>
+        <v>6117</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>正能量智能</t>
+          <t>迎廣</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
         <v/>
       </c>
       <c r="D118" s="2" t="n">
-        <v>338.0453451898773</v>
+        <v>422.0389465904996</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>15.45</v>
+        <v>83</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -6700,16 +6700,16 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>52.3701970010254</v>
+        <v>48.05883440647734</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>16.69749414151812</v>
+        <v>17.88852145437128</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>0.3045345189877272</v>
+        <v>0.7038946590499602</v>
       </c>
       <c r="K118" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L118" s="2" t="n">
         <v>0</v>
@@ -6718,31 +6718,31 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>0.332747769271587</v>
+        <v>-0.2934922617284696</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>5487</v>
+        <v>5272</v>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>通泰</t>
+          <t>笙科</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
         <v/>
       </c>
       <c r="D119" s="2" t="n">
-        <v>319.023534638285</v>
+        <v>417.0167139321436</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>27.65</v>
+        <v>22.35</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
@@ -6753,16 +6753,16 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>49.61595233850798</v>
+        <v>44.44856647069671</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>12.70970798923674</v>
+        <v>11.90070933145323</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>0.4023534638284962</v>
+        <v>0.7016713932143546</v>
       </c>
       <c r="K119" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L119" s="2" t="n">
         <v>0</v>
@@ -6771,31 +6771,31 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>0.0328472334790184</v>
+        <v>0.0113153891480426</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>4588</v>
+        <v>5205</v>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>玖鼎電力</t>
+          <t>中茂</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
         <v/>
       </c>
       <c r="D120" s="2" t="n">
-        <v>318.896943679327</v>
+        <v>412.3850716957859</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>60.2</v>
+        <v>22.75</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -6806,13 +6806,13 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>56.2830972218491</v>
+        <v>48.67112678751445</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>23.43385178364721</v>
+        <v>20.66657669222625</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>1.389694367932697</v>
+        <v>1.238507169578589</v>
       </c>
       <c r="K120" s="2" t="n">
         <v>0</v>
@@ -6824,31 +6824,31 @@
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>0.8621045633493174</v>
+        <v>0.0969563631815353</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>4999</v>
+        <v>6142</v>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>鑫禾</t>
+          <t>友勁</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
         <v/>
       </c>
       <c r="D121" s="2" t="n">
-        <v>314.9238390239365</v>
+        <v>404.3988604874716</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>21.65</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
@@ -6859,13 +6859,13 @@
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>57.912234322352</v>
+        <v>54.40937856429185</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>23.26497946083098</v>
+        <v>23.17079928538596</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>0.992383902393654</v>
+        <v>0.4398860487471609</v>
       </c>
       <c r="K121" s="2" t="n">
         <v>0</v>
@@ -6877,31 +6877,31 @@
         <v>-1</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>0.3195243682897631</v>
+        <v>0.1245082498982358</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>4909</v>
+        <v>5457</v>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>新復興</t>
+          <t>宣德</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
         <v/>
       </c>
       <c r="D122" s="2" t="n">
-        <v>311.465987912004</v>
+        <v>389.9829951185218</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
@@ -6912,13 +6912,13 @@
         <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>39.94566806237798</v>
+        <v>44.21253842659131</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>23.97638049702175</v>
+        <v>20.34484307665447</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>0.6465987912004044</v>
+        <v>0.4982995118521787</v>
       </c>
       <c r="K122" s="2" t="n">
         <v>0</v>
@@ -6930,31 +6930,31 @@
         <v>-1</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>-0.06932684765124961</v>
+        <v>0.3335102639122147</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>5371</v>
+        <v>5234</v>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>中光電</t>
+          <t>達興材料</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
         <v/>
       </c>
       <c r="D123" s="2" t="n">
-        <v>304.2943422095159</v>
+        <v>370.2088109237973</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>73.5</v>
+        <v>403.5</v>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
@@ -6965,13 +6965,13 @@
         <v>0</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>51.78802171867416</v>
+        <v>46.50058993470915</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>14.37701184240316</v>
+        <v>13.70677154588971</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>0.9294342209515928</v>
+        <v>1.020881092379727</v>
       </c>
       <c r="K123" s="2" t="n">
         <v>0</v>
@@ -6983,31 +6983,31 @@
         <v>-1</v>
       </c>
       <c r="N123" s="2" t="n">
-        <v>0.5617420882331645</v>
+        <v>-3.284237034220581</v>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>5302</v>
+        <v>5498</v>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>太欣</t>
+          <t>凱崴</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
         <v/>
       </c>
       <c r="D124" s="2" t="n">
-        <v>303.960616460002</v>
+        <v>369.2950113588209</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>10.7</v>
+        <v>61.8</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
@@ -7018,16 +7018,16 @@
         <v>0</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>48.41671282661751</v>
+        <v>41.05204347878227</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>19.42147517343683</v>
+        <v>14.29748156262141</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>0.896061646000202</v>
+        <v>0.4295011358820925</v>
       </c>
       <c r="K124" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L124" s="2" t="n">
         <v>0</v>
@@ -7036,31 +7036,31 @@
         <v>-1</v>
       </c>
       <c r="N124" s="2" t="n">
-        <v>0.1152207154378518</v>
+        <v>-0.8220805775539193</v>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>5469</v>
+        <v>6136</v>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>瀚宇博</t>
+          <t>富爾特</t>
         </is>
       </c>
       <c r="C125" s="2" t="n">
         <v/>
       </c>
       <c r="D125" s="2" t="n">
-        <v>302.7364508788689</v>
+        <v>367.1025912190054</v>
       </c>
       <c r="E125" s="2" t="n">
-        <v>84</v>
+        <v>25.85</v>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
@@ -7071,16 +7071,16 @@
         <v>0</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>48.35571906869137</v>
+        <v>52.16877597987278</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>17.96944143119556</v>
+        <v>13.65353650784017</v>
       </c>
       <c r="J125" s="2" t="n">
-        <v>0.7736450878868957</v>
+        <v>1.210259121900539</v>
       </c>
       <c r="K125" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L125" s="2" t="n">
         <v>0</v>
@@ -7089,31 +7089,31 @@
         <v>-1</v>
       </c>
       <c r="N125" s="2" t="n">
-        <v>0.5041227576005656</v>
+        <v>0.079432358423753</v>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
-        <v>5272</v>
+        <v>4971</v>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>笙科</t>
+          <t>IET-KY</t>
         </is>
       </c>
       <c r="C126" s="2" t="n">
         <v/>
       </c>
       <c r="D126" s="2" t="n">
-        <v>302.0167139321435</v>
+        <v>361.2039560290591</v>
       </c>
       <c r="E126" s="2" t="n">
-        <v>22.35</v>
+        <v>670</v>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
@@ -7124,13 +7124,13 @@
         <v>0</v>
       </c>
       <c r="H126" s="2" t="n">
-        <v>44.44856639646633</v>
+        <v>44.33791295985692</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>11.90070940491866</v>
+        <v>13.24000974011086</v>
       </c>
       <c r="J126" s="2" t="n">
-        <v>0.7016713932143546</v>
+        <v>1.12039560290591</v>
       </c>
       <c r="K126" s="2" t="n">
         <v>0</v>
@@ -7142,31 +7142,31 @@
         <v>-1</v>
       </c>
       <c r="N126" s="2" t="n">
-        <v>0.0113153890144853</v>
+        <v>-10.05126554889733</v>
       </c>
       <c r="O126" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
-        <v>5450</v>
+        <v>5315</v>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>寶聯通</t>
+          <t>光聯</t>
         </is>
       </c>
       <c r="C127" s="2" t="n">
         <v/>
       </c>
       <c r="D127" s="2" t="n">
-        <v>296.8153507953567</v>
+        <v>358.2957942469156</v>
       </c>
       <c r="E127" s="2" t="n">
-        <v>13.3</v>
+        <v>22.5</v>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
@@ -7177,16 +7177,16 @@
         <v>0</v>
       </c>
       <c r="H127" s="2" t="n">
-        <v>56.22034767857679</v>
+        <v>53.87588995729719</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>17.98291773795428</v>
+        <v>15.04834380980142</v>
       </c>
       <c r="J127" s="2" t="n">
-        <v>0.1815350795356678</v>
+        <v>0.8295794246915653</v>
       </c>
       <c r="K127" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L127" s="2" t="n">
         <v>0</v>
@@ -7195,31 +7195,31 @@
         <v>-1</v>
       </c>
       <c r="N127" s="2" t="n">
-        <v>0.1216290314004033</v>
+        <v>0.1089791984913492</v>
       </c>
       <c r="O127" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
-        <v>5340</v>
+        <v>5244</v>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>建榮</t>
+          <t>弘凱</t>
         </is>
       </c>
       <c r="C128" s="2" t="n">
         <v/>
       </c>
       <c r="D128" s="2" t="n">
-        <v>288.5358628507017</v>
+        <v>355.9208011806687</v>
       </c>
       <c r="E128" s="2" t="n">
-        <v>95.09999999999999</v>
+        <v>38.5</v>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
@@ -7230,13 +7230,13 @@
         <v>0</v>
       </c>
       <c r="H128" s="2" t="n">
-        <v>36.83868698618716</v>
+        <v>45.72963391255384</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>9.572549289765291</v>
+        <v>14.17688512916756</v>
       </c>
       <c r="J128" s="2" t="n">
-        <v>0.8535862850701758</v>
+        <v>0.5920801180668743</v>
       </c>
       <c r="K128" s="2" t="n">
         <v>0</v>
@@ -7248,31 +7248,31 @@
         <v>-1</v>
       </c>
       <c r="N128" s="2" t="n">
-        <v>-0.5449145523704351</v>
+        <v>0.0420901999249145</v>
       </c>
       <c r="O128" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="n">
-        <v>5345</v>
+        <v>5355</v>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>天揚</t>
+          <t>佳總</t>
         </is>
       </c>
       <c r="C129" s="2" t="n">
         <v/>
       </c>
       <c r="D129" s="2" t="n">
-        <v>286.951836457674</v>
+        <v>347.1018404053419</v>
       </c>
       <c r="E129" s="2" t="n">
-        <v>24.2</v>
+        <v>6.7</v>
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
@@ -7283,13 +7283,13 @@
         <v>0</v>
       </c>
       <c r="H129" s="2" t="n">
-        <v>54.4692135698105</v>
+        <v>52.41858135717614</v>
       </c>
       <c r="I129" s="2" t="n">
-        <v>5.107371798973865</v>
+        <v>10.74360225574979</v>
       </c>
       <c r="J129" s="2" t="n">
-        <v>1.195183645767399</v>
+        <v>0.2101840405341876</v>
       </c>
       <c r="K129" s="2" t="n">
         <v>0</v>
@@ -7301,31 +7301,31 @@
         <v>-1</v>
       </c>
       <c r="N129" s="2" t="n">
-        <v>0.5785851295510585</v>
+        <v>0.0333885710288515</v>
       </c>
       <c r="O129" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="n">
-        <v>5460</v>
+        <v>4582</v>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>同協</t>
+          <t>聚恆-創</t>
         </is>
       </c>
       <c r="C130" s="2" t="n">
         <v/>
       </c>
       <c r="D130" s="2" t="n">
-        <v>274.0052978628848</v>
+        <v>345.3080367296231</v>
       </c>
       <c r="E130" s="2" t="n">
-        <v>15.05</v>
+        <v>25.5</v>
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
@@ -7336,13 +7336,13 @@
         <v>0</v>
       </c>
       <c r="H130" s="2" t="n">
-        <v>48.80277112866112</v>
+        <v>39.80376590631051</v>
       </c>
       <c r="I130" s="2" t="n">
-        <v>36.65733971414836</v>
+        <v>18.99539063016912</v>
       </c>
       <c r="J130" s="2" t="n">
-        <v>0.9005297862884771</v>
+        <v>0.5308036729623089</v>
       </c>
       <c r="K130" s="2" t="n">
         <v>0</v>
@@ -7354,31 +7354,31 @@
         <v>-1</v>
       </c>
       <c r="N130" s="2" t="n">
-        <v>-0.0183771881785189</v>
+        <v>-0.1138058335279648</v>
       </c>
       <c r="O130" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="n">
-        <v>6142</v>
+        <v>4977</v>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>友勁</t>
+          <t>眾達-KY</t>
         </is>
       </c>
       <c r="C131" s="2" t="n">
         <v/>
       </c>
       <c r="D131" s="2" t="n">
-        <v>264.3988604874716</v>
+        <v>344.600939549523</v>
       </c>
       <c r="E131" s="2" t="n">
-        <v>8.710000000000001</v>
+        <v>200.5</v>
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
@@ -7389,16 +7389,16 @@
         <v>0</v>
       </c>
       <c r="H131" s="2" t="n">
-        <v>54.40937848015309</v>
+        <v>47.24904911894719</v>
       </c>
       <c r="I131" s="2" t="n">
-        <v>23.17079938308916</v>
+        <v>14.87835471722525</v>
       </c>
       <c r="J131" s="2" t="n">
-        <v>0.4398860487471609</v>
+        <v>0.460093954952304</v>
       </c>
       <c r="K131" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L131" s="2" t="n">
         <v>0</v>
@@ -7407,31 +7407,31 @@
         <v>-1</v>
       </c>
       <c r="N131" s="2" t="n">
-        <v>0.1245082498715243</v>
+        <v>-2.099727983847436</v>
       </c>
       <c r="O131" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="n">
-        <v>4994</v>
+        <v>4909</v>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>傳奇</t>
+          <t>新復興</t>
         </is>
       </c>
       <c r="C132" s="2" t="n">
         <v/>
       </c>
       <c r="D132" s="2" t="n">
-        <v>258.7005427319943</v>
+        <v>311.465987912004</v>
       </c>
       <c r="E132" s="2" t="n">
-        <v>87.59999999999999</v>
+        <v>50</v>
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
@@ -7442,16 +7442,16 @@
         <v>0</v>
       </c>
       <c r="H132" s="2" t="n">
-        <v>37.01075227482981</v>
+        <v>39.9456682685237</v>
       </c>
       <c r="I132" s="2" t="n">
-        <v>24.35971903454616</v>
+        <v>23.9763806814963</v>
       </c>
       <c r="J132" s="2" t="n">
-        <v>0.3700542731994328</v>
+        <v>0.6465987912004044</v>
       </c>
       <c r="K132" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L132" s="2" t="n">
         <v>0</v>
@@ -7460,31 +7460,31 @@
         <v>-1</v>
       </c>
       <c r="N132" s="2" t="n">
-        <v>-0.2867316017866845</v>
+        <v>-0.0693268473459749</v>
       </c>
       <c r="O132" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="n">
-        <v>5457</v>
+        <v>5292</v>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>宣德</t>
+          <t>華懋</t>
         </is>
       </c>
       <c r="C133" s="2" t="n">
         <v/>
       </c>
       <c r="D133" s="2" t="n">
-        <v>249.9829951185218</v>
+        <v>309.8772143217579</v>
       </c>
       <c r="E133" s="2" t="n">
-        <v>31</v>
+        <v>216.5</v>
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
@@ -7495,13 +7495,13 @@
         <v>0</v>
       </c>
       <c r="H133" s="2" t="n">
-        <v>44.21253834138736</v>
+        <v>42.48176264545555</v>
       </c>
       <c r="I133" s="2" t="n">
-        <v>20.34484297728629</v>
+        <v>13.65153408632618</v>
       </c>
       <c r="J133" s="2" t="n">
-        <v>0.4982995118521787</v>
+        <v>0.9877214321757932</v>
       </c>
       <c r="K133" s="2" t="n">
         <v>0</v>
@@ -7513,31 +7513,31 @@
         <v>-1</v>
       </c>
       <c r="N133" s="2" t="n">
-        <v>0.3335102638740528</v>
+        <v>-0.528496666483951</v>
       </c>
       <c r="O133" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="n">
-        <v>5432</v>
+        <v>5278</v>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>新門</t>
+          <t>尚凡</t>
         </is>
       </c>
       <c r="C134" s="2" t="n">
         <v/>
       </c>
       <c r="D134" s="2" t="n">
-        <v>246.7947209422355</v>
+        <v>304.893650620496</v>
       </c>
       <c r="E134" s="2" t="n">
-        <v>135.5</v>
+        <v>23.3</v>
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
@@ -7548,16 +7548,16 @@
         <v>0</v>
       </c>
       <c r="H134" s="2" t="n">
-        <v>45.44972164599066</v>
+        <v>48.02965026766185</v>
       </c>
       <c r="I134" s="2" t="n">
-        <v>12.10200500601817</v>
+        <v>13.06261872472616</v>
       </c>
       <c r="J134" s="2" t="n">
-        <v>1.679472094223546</v>
+        <v>0.4893650620495967</v>
       </c>
       <c r="K134" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L134" s="2" t="n">
         <v>0</v>
@@ -7566,31 +7566,31 @@
         <v>-1</v>
       </c>
       <c r="N134" s="2" t="n">
-        <v>-1.015364379627778</v>
+        <v>0.0687143145130112</v>
       </c>
       <c r="O134" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="n">
-        <v>5315</v>
+        <v>5302</v>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>光聯</t>
+          <t>太欣</t>
         </is>
       </c>
       <c r="C135" s="2" t="n">
         <v/>
       </c>
       <c r="D135" s="2" t="n">
-        <v>243.2957942469156</v>
+        <v>303.960616460002</v>
       </c>
       <c r="E135" s="2" t="n">
-        <v>22.5</v>
+        <v>10.7</v>
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
@@ -7601,16 +7601,16 @@
         <v>0</v>
       </c>
       <c r="H135" s="2" t="n">
-        <v>53.87588977332832</v>
+        <v>48.41671281674367</v>
       </c>
       <c r="I135" s="2" t="n">
-        <v>15.04834371117224</v>
+        <v>19.4214751930101</v>
       </c>
       <c r="J135" s="2" t="n">
-        <v>0.8295794246915653</v>
+        <v>0.896061646000202</v>
       </c>
       <c r="K135" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L135" s="2" t="n">
         <v>0</v>
@@ -7619,31 +7619,31 @@
         <v>-1</v>
       </c>
       <c r="N135" s="2" t="n">
-        <v>0.108979198462732</v>
+        <v>0.1152207155103533</v>
       </c>
       <c r="O135" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="n">
-        <v>5244</v>
+        <v>5469</v>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>弘凱</t>
+          <t>瀚宇博</t>
         </is>
       </c>
       <c r="C136" s="2" t="n">
         <v/>
       </c>
       <c r="D136" s="2" t="n">
-        <v>240.9208011806687</v>
+        <v>302.7364508788689</v>
       </c>
       <c r="E136" s="2" t="n">
-        <v>38.5</v>
+        <v>84</v>
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
@@ -7654,13 +7654,13 @@
         <v>0</v>
       </c>
       <c r="H136" s="2" t="n">
-        <v>45.72963383875948</v>
+        <v>48.35571913555015</v>
       </c>
       <c r="I136" s="2" t="n">
-        <v>14.1768851798391</v>
+        <v>17.96944136434124</v>
       </c>
       <c r="J136" s="2" t="n">
-        <v>0.5920801180668743</v>
+        <v>0.7736450878868957</v>
       </c>
       <c r="K136" s="2" t="n">
         <v>0</v>
@@ -7672,31 +7672,31 @@
         <v>-1</v>
       </c>
       <c r="N136" s="2" t="n">
-        <v>0.0420901996196502</v>
+        <v>0.5041227576864324</v>
       </c>
       <c r="O136" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="n">
-        <v>5258</v>
+        <v>5340</v>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>虹堡</t>
+          <t>建榮</t>
         </is>
       </c>
       <c r="C137" s="2" t="n">
         <v/>
       </c>
       <c r="D137" s="2" t="n">
-        <v>237.861105328293</v>
+        <v>288.5358628507017</v>
       </c>
       <c r="E137" s="2" t="n">
-        <v>50.3</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
@@ -7707,13 +7707,13 @@
         <v>0</v>
       </c>
       <c r="H137" s="2" t="n">
-        <v>43.49684162727912</v>
+        <v>36.83868699875429</v>
       </c>
       <c r="I137" s="2" t="n">
-        <v>22.94638614653056</v>
+        <v>9.572549193023455</v>
       </c>
       <c r="J137" s="2" t="n">
-        <v>0.2861105328293002</v>
+        <v>0.8535862850701758</v>
       </c>
       <c r="K137" s="2" t="n">
         <v>0</v>
@@ -7725,31 +7725,31 @@
         <v>-1</v>
       </c>
       <c r="N137" s="2" t="n">
-        <v>-0.8013812900266558</v>
+        <v>-0.5449145522750296</v>
       </c>
       <c r="O137" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="n">
-        <v>5292</v>
+        <v>5460</v>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>華懋</t>
+          <t>同協</t>
         </is>
       </c>
       <c r="C138" s="2" t="n">
         <v/>
       </c>
       <c r="D138" s="2" t="n">
-        <v>234.8772143217579</v>
+        <v>274.0052978628848</v>
       </c>
       <c r="E138" s="2" t="n">
-        <v>216.5</v>
+        <v>15.05</v>
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
@@ -7760,13 +7760,13 @@
         <v>0</v>
       </c>
       <c r="H138" s="2" t="n">
-        <v>42.48176256568646</v>
+        <v>48.80277114858559</v>
       </c>
       <c r="I138" s="2" t="n">
-        <v>13.6515341106748</v>
+        <v>36.65733966066201</v>
       </c>
       <c r="J138" s="2" t="n">
-        <v>0.9877214321757932</v>
+        <v>0.9005297862884771</v>
       </c>
       <c r="K138" s="2" t="n">
         <v>0</v>
@@ -7778,31 +7778,31 @@
         <v>-1</v>
       </c>
       <c r="N138" s="2" t="n">
-        <v>-0.5284966658161823</v>
+        <v>-0.0183771880926602</v>
       </c>
       <c r="O138" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="n">
-        <v>5355</v>
+        <v>4994</v>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>佳總</t>
+          <t>傳奇</t>
         </is>
       </c>
       <c r="C139" s="2" t="n">
         <v/>
       </c>
       <c r="D139" s="2" t="n">
-        <v>232.1018404053419</v>
+        <v>258.7005427319943</v>
       </c>
       <c r="E139" s="2" t="n">
-        <v>6.7</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
@@ -7813,13 +7813,13 @@
         <v>0</v>
       </c>
       <c r="H139" s="2" t="n">
-        <v>52.41858126604044</v>
+        <v>37.01075242914553</v>
       </c>
       <c r="I139" s="2" t="n">
-        <v>10.7436022335161</v>
+        <v>24.35971900306212</v>
       </c>
       <c r="J139" s="2" t="n">
-        <v>0.2101840405341876</v>
+        <v>0.3700542731994328</v>
       </c>
       <c r="K139" s="2" t="n">
         <v>0</v>
@@ -7831,31 +7831,31 @@
         <v>-1</v>
       </c>
       <c r="N139" s="2" t="n">
-        <v>0.0333885710002326</v>
+        <v>-0.2867316022255064</v>
       </c>
       <c r="O139" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="n">
-        <v>4934</v>
+        <v>5432</v>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>太極</t>
+          <t>新門</t>
         </is>
       </c>
       <c r="C140" s="2" t="n">
         <v/>
       </c>
       <c r="D140" s="2" t="n">
-        <v>228.6008675789229</v>
+        <v>246.7947209422355</v>
       </c>
       <c r="E140" s="2" t="n">
-        <v>16.55</v>
+        <v>135.5</v>
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
@@ -7866,16 +7866,16 @@
         <v>0</v>
       </c>
       <c r="H140" s="2" t="n">
-        <v>44.19520810176167</v>
+        <v>45.44972166612795</v>
       </c>
       <c r="I140" s="2" t="n">
-        <v>12.8880720397822</v>
+        <v>12.10200502093874</v>
       </c>
       <c r="J140" s="2" t="n">
-        <v>0.8600867578922894</v>
+        <v>1.679472094223546</v>
       </c>
       <c r="K140" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L140" s="2" t="n">
         <v>0</v>
@@ -7884,31 +7884,31 @@
         <v>-1</v>
       </c>
       <c r="N140" s="2" t="n">
-        <v>-0.0630665603012022</v>
+        <v>-1.015364378387623</v>
       </c>
       <c r="O140" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="n">
-        <v>4968</v>
+        <v>5258</v>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>立積</t>
+          <t>虹堡</t>
         </is>
       </c>
       <c r="C141" s="2" t="n">
         <v/>
       </c>
       <c r="D141" s="2" t="n">
-        <v>228.1320051900634</v>
+        <v>237.861105328293</v>
       </c>
       <c r="E141" s="2" t="n">
-        <v>113.5</v>
+        <v>50.3</v>
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
@@ -7919,13 +7919,13 @@
         <v>0</v>
       </c>
       <c r="H141" s="2" t="n">
-        <v>45.03877655114959</v>
+        <v>43.49684154370061</v>
       </c>
       <c r="I141" s="2" t="n">
-        <v>17.05202311613148</v>
+        <v>22.94638632623453</v>
       </c>
       <c r="J141" s="2" t="n">
-        <v>0.8132005190063368</v>
+        <v>0.2861105328293002</v>
       </c>
       <c r="K141" s="2" t="n">
         <v>0</v>
@@ -7937,31 +7937,31 @@
         <v>-1</v>
       </c>
       <c r="N141" s="2" t="n">
-        <v>-0.288392389537029</v>
+        <v>-0.8013812890536044</v>
       </c>
       <c r="O141" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="n">
-        <v>4903</v>
+        <v>5468</v>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>聯光通</t>
+          <t>凱鈺</t>
         </is>
       </c>
       <c r="C142" s="2" t="n">
         <v/>
       </c>
       <c r="D142" s="2" t="n">
-        <v>212.9381617498328</v>
+        <v>237.4384834808388</v>
       </c>
       <c r="E142" s="2" t="n">
-        <v>44.1</v>
+        <v>17.8</v>
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
@@ -7972,16 +7972,16 @@
         <v>0</v>
       </c>
       <c r="H142" s="2" t="n">
-        <v>44.94392406450581</v>
+        <v>49.63004142423006</v>
       </c>
       <c r="I142" s="2" t="n">
-        <v>12.51048728649823</v>
+        <v>10.66536958880612</v>
       </c>
       <c r="J142" s="2" t="n">
-        <v>0.2938161749832749</v>
+        <v>0.7438483480838779</v>
       </c>
       <c r="K142" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L142" s="2" t="n">
         <v>0</v>
@@ -7990,31 +7990,31 @@
         <v>-1</v>
       </c>
       <c r="N142" s="2" t="n">
-        <v>-0.1157270725998132</v>
+        <v>0.0575069640527296</v>
       </c>
       <c r="O142" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="n">
-        <v>4943</v>
+        <v>4934</v>
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>康控-KY</t>
+          <t>太極</t>
         </is>
       </c>
       <c r="C143" s="2" t="n">
         <v/>
       </c>
       <c r="D143" s="2" t="n">
-        <v>173.4937587800413</v>
+        <v>228.6008675789229</v>
       </c>
       <c r="E143" s="2" t="n">
-        <v>8.9</v>
+        <v>16.55</v>
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
@@ -8025,13 +8025,13 @@
         <v>0</v>
       </c>
       <c r="H143" s="2" t="n">
-        <v>42.96023226307921</v>
+        <v>44.19520818053854</v>
       </c>
       <c r="I143" s="2" t="n">
-        <v>18.93459415528168</v>
+        <v>12.88807192636806</v>
       </c>
       <c r="J143" s="2" t="n">
-        <v>0.349375878004134</v>
+        <v>0.8600867578922894</v>
       </c>
       <c r="K143" s="2" t="n">
         <v>0</v>
@@ -8043,31 +8043,31 @@
         <v>-1</v>
       </c>
       <c r="N143" s="2" t="n">
-        <v>0.0455931639001387</v>
+        <v>-0.0630665602420554</v>
       </c>
       <c r="O143" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="n">
-        <v>5278</v>
+        <v>4968</v>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>尚凡</t>
+          <t>立積</t>
         </is>
       </c>
       <c r="C144" s="2" t="n">
         <v/>
       </c>
       <c r="D144" s="2" t="n">
-        <v>164.893650620496</v>
+        <v>228.1320051900633</v>
       </c>
       <c r="E144" s="2" t="n">
-        <v>23.3</v>
+        <v>113.5</v>
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
@@ -8078,13 +8078,13 @@
         <v>0</v>
       </c>
       <c r="H144" s="2" t="n">
-        <v>48.02965021429709</v>
+        <v>45.03877648843925</v>
       </c>
       <c r="I144" s="2" t="n">
-        <v>13.06261863664625</v>
+        <v>17.05202316971868</v>
       </c>
       <c r="J144" s="2" t="n">
-        <v>0.4893650620495967</v>
+        <v>0.8132005190063368</v>
       </c>
       <c r="K144" s="2" t="n">
         <v>0</v>
@@ -8096,31 +8096,31 @@
         <v>-1</v>
       </c>
       <c r="N144" s="2" t="n">
-        <v>0.06871431454162991</v>
+        <v>-0.2883923878198922</v>
       </c>
       <c r="O144" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="n">
-        <v>5222</v>
+        <v>4903</v>
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>全訊</t>
+          <t>聯光通</t>
         </is>
       </c>
       <c r="C145" s="2" t="n">
         <v/>
       </c>
       <c r="D145" s="2" t="n">
-        <v>157.7947749134107</v>
+        <v>212.9381617498328</v>
       </c>
       <c r="E145" s="2" t="n">
-        <v>121.5</v>
+        <v>44.1</v>
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
@@ -8131,16 +8131,16 @@
         <v>0</v>
       </c>
       <c r="H145" s="2" t="n">
-        <v>39.81639093487325</v>
+        <v>44.94392412937729</v>
       </c>
       <c r="I145" s="2" t="n">
-        <v>12.63031823930907</v>
+        <v>12.51048722834244</v>
       </c>
       <c r="J145" s="2" t="n">
-        <v>0.7794774913410736</v>
+        <v>0.2938161749832749</v>
       </c>
       <c r="K145" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L145" s="2" t="n">
         <v>0</v>
@@ -8149,31 +8149,31 @@
         <v>-1</v>
       </c>
       <c r="N145" s="2" t="n">
-        <v>-0.1273985714255427</v>
+        <v>-0.1157270724185582</v>
       </c>
       <c r="O145" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="n">
-        <v>5314</v>
+        <v>4943</v>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>世紀*</t>
+          <t>康控-KY</t>
         </is>
       </c>
       <c r="C146" s="2" t="n">
         <v/>
       </c>
       <c r="D146" s="2" t="n">
-        <v>156.931951291427</v>
+        <v>173.4937587800413</v>
       </c>
       <c r="E146" s="2" t="n">
-        <v>61.2</v>
+        <v>8.9</v>
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
@@ -8184,13 +8184,13 @@
         <v>0</v>
       </c>
       <c r="H146" s="2" t="n">
-        <v>46.24586659574092</v>
+        <v>42.96023194135884</v>
       </c>
       <c r="I146" s="2" t="n">
-        <v>6.340655460154522</v>
+        <v>18.93459423085304</v>
       </c>
       <c r="J146" s="2" t="n">
-        <v>0.6931951291427022</v>
+        <v>0.349375878004134</v>
       </c>
       <c r="K146" s="2" t="n">
         <v>0</v>
@@ -8202,31 +8202,31 @@
         <v>-1</v>
       </c>
       <c r="N146" s="2" t="n">
-        <v>0.3574134851947814</v>
+        <v>0.0455931640336954</v>
       </c>
       <c r="O146" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="n">
-        <v>4582</v>
+        <v>5222</v>
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>聚恆-創</t>
+          <t>全訊</t>
         </is>
       </c>
       <c r="C147" s="2" t="n">
         <v/>
       </c>
       <c r="D147" s="2" t="n">
-        <v>155.3080367296231</v>
+        <v>157.7947749134107</v>
       </c>
       <c r="E147" s="2" t="n">
-        <v>25.5</v>
+        <v>121.5</v>
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
@@ -8237,13 +8237,13 @@
         <v>0</v>
       </c>
       <c r="H147" s="2" t="n">
-        <v>39.80376592535151</v>
+        <v>39.81639097762101</v>
       </c>
       <c r="I147" s="2" t="n">
-        <v>18.9953906180798</v>
+        <v>12.63031811586702</v>
       </c>
       <c r="J147" s="2" t="n">
-        <v>0.5308036729623089</v>
+        <v>0.7794774913410736</v>
       </c>
       <c r="K147" s="2" t="n">
         <v>0</v>
@@ -8255,31 +8255,31 @@
         <v>-1</v>
       </c>
       <c r="N147" s="2" t="n">
-        <v>-0.1138058335947427</v>
+        <v>-0.1273985711393361</v>
       </c>
       <c r="O147" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="n">
-        <v>5468</v>
+        <v>5314</v>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>凱鈺</t>
+          <t>世紀*</t>
         </is>
       </c>
       <c r="C148" s="2" t="n">
         <v/>
       </c>
       <c r="D148" s="2" t="n">
-        <v>97.43848348083878</v>
+        <v>156.931951291427</v>
       </c>
       <c r="E148" s="2" t="n">
-        <v>17.8</v>
+        <v>61.2</v>
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
@@ -8290,13 +8290,13 @@
         <v>0</v>
       </c>
       <c r="H148" s="2" t="n">
-        <v>49.6300414342407</v>
+        <v>46.24586651102661</v>
       </c>
       <c r="I148" s="2" t="n">
-        <v>10.66536957915997</v>
+        <v>6.340655461237838</v>
       </c>
       <c r="J148" s="2" t="n">
-        <v>0.7438483480838779</v>
+        <v>0.6931951291427022</v>
       </c>
       <c r="K148" s="2" t="n">
         <v>0</v>
@@ -8308,11 +8308,11 @@
         <v>-1</v>
       </c>
       <c r="N148" s="2" t="n">
-        <v>0.0575069639764117</v>
+        <v>0.3574134863013904</v>
       </c>
       <c r="O148" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
